--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\PHD files\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\phd\Battery_Dataset_Webpage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1BACE6-5835-48E7-968C-61D8C7A5E907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5A5CC1-4773-4D9E-839F-CE44BD2086E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="545">
   <si>
     <t>No.</t>
   </si>
@@ -1575,25 +1575,125 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>链接1：https://calce.umd.edu/battery-data 链接2：https://web.calce.umd.edu/batteries/data/</t>
+    <t>https://calce.umd.edu/battery-data</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Huazhong University of Science and Technology</t>
-  </si>
-  <si>
-    <t>https://data.mendeley.com/datasets/nsc7hnsg4s/2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">A dataset with 77 LFP/graphite cells (1.1 Ah nominal capacity and 3.3 V nominal voltage). The cells were cycled with an identical charge protocol but different multi-stage discharge protocols at a constant temperature of 30°C. </t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ye Yuan
-Guijun Ma
-Songpei Xu</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>Multi-stage Discharge Protocol LFP Dataset (77 cells)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.17632/nsc7hnsg4s.2</t>
+  </si>
+  <si>
+    <t>Y. Yang et al. (Authors’ Lab)</t>
+  </si>
+  <si>
+    <t>18650 cylindrical (APR18650M1A)</t>
+  </si>
+  <si>
+    <t>LFP/Graphite, 3.3 V nominal</t>
+  </si>
+  <si>
+    <t>A123</t>
+  </si>
+  <si>
+    <t>Voltage, Current, Capacity</t>
+  </si>
+  <si>
+    <t>Identical fast-charging; fully different multi-stage discharge protocols; EOL at 80% capacity</t>
+  </si>
+  <si>
+    <t>30°C (constant)</t>
+  </si>
+  <si>
+    <t>Charge: 5C (0–80% SOC) + 1C to 3.6V + CV (C/20 cutoff); Discharge: 4-stage CC (last stage 1C to 2V)</t>
+  </si>
+  <si>
+    <t>Yes (1100–2700 cycles)</t>
+  </si>
+  <si>
+    <t>Multi-stage discharge variability; 30 s rest between stages</t>
+  </si>
+  <si>
+    <t>Not specified (available via Mendeley)</t>
+  </si>
+  <si>
+    <t>146,122 total charge–discharge cycles</t>
+  </si>
+  <si>
+    <t>77 cells (55 training, 22 testing)</t>
+  </si>
+  <si>
+    <t>Proposed in current study</t>
+  </si>
+  <si>
+    <t>SOH estimation, capacity prediction, RUL prediction, personalized health management</t>
+  </si>
+  <si>
+    <t>Removal of 3 faulty cells; fixed SOC window selection</t>
+  </si>
+  <si>
+    <t>Charge segment 80% SOC → first 3.6V; V, Q, ΔV(i−10), ΔQ(i−10); interpolated to 100 points; 30 recent cycles sampled to 10</t>
+  </si>
+  <si>
+    <t>Large-scale dataset focusing on discharge variability; suitable for transfer learning research</t>
+  </si>
+  <si>
+    <t>Severson et al.</t>
+  </si>
+  <si>
+    <t>Not specified in current paper</t>
+  </si>
+  <si>
+    <t>Preger et al. NMC Dataset (Battery Archive)</t>
+  </si>
+  <si>
+    <t>Preger et al.</t>
+  </si>
+  <si>
+    <t>18650 cylindrical (LG 18650HG2)</t>
+  </si>
+  <si>
+    <t>NMC/Graphite, 3.6 V nominal, 4.2 V charge limit</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>Cycling data (voltage, current, capacity implied), multi-temperature testing</t>
+  </si>
+  <si>
+    <t>Identical charge protocol; multiple discharge rates</t>
+  </si>
+  <si>
+    <t>15°C / 25°C / 35°C</t>
+  </si>
+  <si>
+    <t>Charge: 0.5C to 4.2V + CV; Discharge: 0.5C / 1C / 2C / 3C to 2V</t>
+  </si>
+  <si>
+    <t>Yes (380–1321 cycles)</t>
+  </si>
+  <si>
+    <t>Cross-chemistry dataset; multi-temperature, multi-rate</t>
+  </si>
+  <si>
+    <t>Not specified (Battery Archive)</t>
+  </si>
+  <si>
+    <t>22 cells</t>
+  </si>
+  <si>
+    <t>Preger et al.; used in cross-chemistry studies</t>
+  </si>
+  <si>
+    <t>Cross-chemistry SOH/RUL prediction, temperature impact studies</t>
+  </si>
+  <si>
+    <t>Fixed SOC window (80% SOC → first 4.2V); interpolation to unified length</t>
+  </si>
+  <si>
+    <t>Used for cross-chemistry transfer learning (Task C)</t>
   </si>
 </sst>
 </file>
@@ -1688,7 +1788,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1721,9 +1821,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2021,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr defaultColWidth="27.25" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.25" style="4"/>
@@ -2677,7 +2774,9 @@
       <c r="C9" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="5" t="s">
+        <v>526</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>54</v>
       </c>
@@ -4025,28 +4124,171 @@
         <v>503</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="98" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="56" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="5" t="s">
         <v>507</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>509</v>
       </c>
+      <c r="G26" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="I26" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="S26" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="U26" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="V26" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="W26" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="X26" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="Y26" s="5" t="s">
+        <v>463</v>
+      </c>
       <c r="Z26" s="5" t="s">
-        <v>508</v>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" ht="42" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="I27" s="5">
+        <v>3</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="S27" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="T27" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="U27" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="V27" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="W27" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="X27" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="Y27" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z27" s="5" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" location="battery" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C5" r:id="rId2" display="https://calce.umd.edu/battery-data " xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="C7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="C8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
@@ -4070,9 +4312,8 @@
     <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
     <hyperlink ref="D13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
     <hyperlink ref="D23" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C26" r:id="rId26" xr:uid="{CBD0B235-B924-4D7F-B0D2-47F39D74B434}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>